--- a/dados/enviadas/Starmac.xlsx
+++ b/dados/enviadas/Starmac.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$J$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$J$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="[$R$-416] #,##0.00"/>
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
     <numFmt numFmtId="165" formatCode="DD/MM/YYYY"/>
   </numFmts>
   <fonts count="3">
@@ -74,13 +74,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -451,173 +449,125 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
     <col width="27" customWidth="1" min="3" max="3"/>
     <col width="23" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="55" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="23" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
     <col width="60" customWidth="1" min="9" max="9"/>
-    <col width="59" customWidth="1" min="10" max="10"/>
+    <col width="58" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>CLIENTE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>ITEM</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>MODALIDADE</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>VALOR_ESTIMADO</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>ORGAO</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>DATA_DISPUTA</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="3" t="inlineStr">
         <is>
           <t>PORTAL</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="3" t="inlineStr">
         <is>
           <t>LINK_PORTAL</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="J1" s="3" t="inlineStr">
         <is>
           <t>LINK_PNCP</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>Starmac</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>024Pe/2026/2026</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>Bombas submersas</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>90070/2026</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>Motobombas submersíveis</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>Pregão - Eletrônico</t>
         </is>
       </c>
-      <c r="E2" s="4" t="n">
-        <v>95751.41</v>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>MUNICIPIO DE SAO GONCALO DOS CAMPOS</t>
-        </is>
-      </c>
-      <c r="G2" s="5" t="inlineStr">
-        <is>
-          <t>09/10/2026</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>Novo Banco do Brasil</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>https://licitacoes-e2.bb.com.br/aop-inter-estatico/visualizar-processo-publico/1101505</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>https://pncp.gov.br/app/editais/14060602000149/2026/120</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>Starmac</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>90070/2026</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>Motobombas submersíveis</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>Pregão - Eletrônico</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>Sigiloso</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>COMPANHIA DE AGUAS E ESGOTOS DO RIO GRANDE DO NORTE</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr"/>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="G2" s="5" t="n">
+        <v>46309.375</v>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
         <is>
           <t>ComprasGov</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="I2" s="4" t="inlineStr">
         <is>
           <t>https://cnetmobile.estaleiro.serpro.gov.br/comprasnet-web/public/landing?destino=acompanhamento-compra&amp;compra=92577705900702026</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="J2" s="4" t="inlineStr">
         <is>
           <t>https://pncp.gov.br/app/editais/08334385000135/2026/49</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J3"/>
+  <autoFilter ref="A1:J2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>